--- a/satisfaction_surveys/010_vendor_invoice_experience_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/010_vendor_invoice_experience_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>vendor_invoicesurvey</t>
+          <t>satisfaction_with_invoices</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>vendor_experience</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vendor_satisfaction</t>
+          <t>satisfaction_with_vendor_team</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>payment_timeliness</t>
+          <t>payment_timeliness_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How timely are our payments?</t>
+          <t>Payment Timeliness 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>vendor_relationship</t>
+          <t>vendor_relationship_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What kind of relationship do you have with our vendor team?</t>
+          <t>Vendor Relationship 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,177 +957,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>vendor_support</t>
+          <t>vendor_support_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How supportive is the vendor team in answering your questions?</t>
+          <t>Vendor Support 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Is there anything else you'd like to comment on or tell us about?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>payment_frequency</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>How often do you receive payments from our company?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>vendor_experience</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>How would you rate your overall experience with our vendor team?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>invoice_format</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How often do you like the format of our invoices?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>communication_effectiveness</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>How effective is our communication in addressing your concerns?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>vendor_satisfaction</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>How satisfied are you with our vendor team?</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>payment_punctuality</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>How punctual are our payments?</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1144,10 +983,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1682,7 +1521,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vendor_experience_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1699,7 +1538,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vendor_experience_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1716,7 +1555,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vendor_experience_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1733,7 +1572,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vendor_experience_choices</t>
+          <t>overall_experience_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1852,7 +1691,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>vendor_satisfaction_choices</t>
+          <t>satisfaction_with_vendor_team_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1869,7 +1708,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vendor_satisfaction_choices</t>
+          <t>satisfaction_with_vendor_team_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1886,7 +1725,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>vendor_satisfaction_choices</t>
+          <t>satisfaction_with_vendor_team_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1954,7 +1793,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>payment_timeliness_choices</t>
+          <t>payment_timeliness_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1971,7 +1810,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>payment_timeliness_choices</t>
+          <t>payment_timeliness_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1988,7 +1827,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>payment_timeliness_choices</t>
+          <t>payment_timeliness_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2005,7 +1844,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vendor_relationship_choices</t>
+          <t>vendor_relationship_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2022,7 +1861,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>vendor_relationship_choices</t>
+          <t>vendor_relationship_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2039,7 +1878,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>vendor_relationship_choices</t>
+          <t>vendor_relationship_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2056,7 +1895,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vendor_support_choices</t>
+          <t>vendor_support_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2073,7 +1912,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vendor_support_choices</t>
+          <t>vendor_support_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2090,7 +1929,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>vendor_support_choices</t>
+          <t>vendor_support_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2101,346 +1940,6 @@
       <c r="C56" t="inlineStr">
         <is>
           <t>Not very supportive</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>payment_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>every_time</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Every time</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>payment_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>most_of_the_time</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Most of the time</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>payment_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>some_of_the_time</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Some of the time</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>payment_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>vendor_experience_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>vendor_experience_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>vendor_experience_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>vendor_experience_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>invoice_format_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>very_much</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Very much</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>invoice_format_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>somewhat</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Somewhat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>invoice_format_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>not_very_much</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Not very much</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>communication_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>very_effective</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Very effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>communication_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>somewhat_effective</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Somewhat effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>communication_effectiveness_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>not_very_effective</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Not very effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>vendor_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>very_satisfied</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>vendor_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>somewhat_satisfied</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Somewhat satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>vendor_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>not_very_satisfied</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Not very satisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>payment_punctuality_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>very_punctual</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Very punctual</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>payment_punctuality_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>somewhat_punctual</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Somewhat punctual</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>payment_punctuality_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>not_very_punctual</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Not very punctual</t>
         </is>
       </c>
     </row>
